--- a/Інтелектуальний аналіз даних/Goretsky_lab1-2.xlsx
+++ b/Інтелектуальний аналіз даних/Goretsky_lab1-2.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Макс\Desktop\навчання\Інтелектуальний аналіз даних\лаб1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\education\Інтелектуальний аналіз даних\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BB7836-CAA1-48E6-A607-C376B50A3330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F3CA54-0CBD-42A6-A944-0E350E72C718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11385" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Постановка задачі 1" sheetId="3" r:id="rId1"/>
-    <sheet name="Завдання 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Постановка задачі 2" sheetId="4" r:id="rId3"/>
-    <sheet name="Завдання 2" sheetId="1" r:id="rId4"/>
+    <sheet name="приклад" sheetId="5" r:id="rId2"/>
+    <sheet name="Завдання 1" sheetId="2" r:id="rId3"/>
+    <sheet name="Постановка задачі 2" sheetId="4" r:id="rId4"/>
+    <sheet name="Завдання 2" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
   <si>
     <t>Коеф-т кореляції Rxy =</t>
   </si>
@@ -395,6 +396,15 @@
       </rPr>
       <t xml:space="preserve"> Перевірка значущості кореляції через критерій Стьюдента</t>
     </r>
+  </si>
+  <si>
+    <t>Завдання 1. Постановка задачі: для виявлення зв’язку між ознаками у та х проведено серію експериментів і отримано такі результати:</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
   </si>
 </sst>
 </file>
@@ -422,6 +432,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -580,59 +591,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -911,47 +931,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF486E6F-2E7D-45B7-8BDC-2BDC2E25A7FD}">
   <dimension ref="A1:V3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" customWidth="1"/>
-    <col min="9" max="9" width="0.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="0.33203125" hidden="1" customWidth="1"/>
-    <col min="11" max="13" width="8.88671875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="5.5546875" hidden="1" customWidth="1"/>
-    <col min="15" max="20" width="8.88671875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="5.109375" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="9.6640625" customWidth="1"/>
-    <col min="23" max="23" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="0.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="0.28515625" hidden="1" customWidth="1"/>
+    <col min="11" max="13" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" hidden="1" customWidth="1"/>
+    <col min="15" max="20" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="5.140625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" customWidth="1"/>
+    <col min="23" max="23" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="84.6" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-    </row>
-    <row r="3" spans="1:22" ht="14.4" customHeight="1"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+    </row>
+    <row r="3" spans="1:22" ht="14.45" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
@@ -961,29 +981,659 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6D5D6A-D245-496D-8698-D5A4B5FB52AA}">
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="25"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="26"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="27"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="23">
+        <v>5</v>
+      </c>
+      <c r="C3" s="23">
+        <v>4</v>
+      </c>
+      <c r="D3" s="23">
+        <v>3</v>
+      </c>
+      <c r="E3" s="23">
+        <v>7</v>
+      </c>
+      <c r="F3" s="23">
+        <v>13</v>
+      </c>
+      <c r="G3" s="23">
+        <v>11</v>
+      </c>
+      <c r="H3" s="23">
+        <v>23</v>
+      </c>
+      <c r="I3" s="23">
+        <v>28</v>
+      </c>
+      <c r="J3" s="23">
+        <v>18</v>
+      </c>
+      <c r="K3" s="23">
+        <v>9</v>
+      </c>
+      <c r="L3" s="23">
+        <v>12</v>
+      </c>
+      <c r="M3" s="23">
+        <v>13</v>
+      </c>
+      <c r="N3" s="27"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A4" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="29">
+        <v>64</v>
+      </c>
+      <c r="C4" s="29">
+        <v>71</v>
+      </c>
+      <c r="D4" s="29">
+        <v>54</v>
+      </c>
+      <c r="E4" s="29">
+        <v>71</v>
+      </c>
+      <c r="F4" s="29">
+        <v>93</v>
+      </c>
+      <c r="G4" s="29">
+        <v>76</v>
+      </c>
+      <c r="H4" s="29">
+        <v>87</v>
+      </c>
+      <c r="I4" s="29">
+        <v>109</v>
+      </c>
+      <c r="J4" s="29">
+        <v>83</v>
+      </c>
+      <c r="K4" s="29">
+        <v>75</v>
+      </c>
+      <c r="L4" s="29">
+        <v>79</v>
+      </c>
+      <c r="M4" s="29">
+        <v>87</v>
+      </c>
+      <c r="N4" s="30"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>64</v>
+      </c>
+      <c r="C8">
+        <f>A8-$A$10</f>
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <f>B8-$B$21</f>
+        <v>-15.083333333333329</v>
+      </c>
+      <c r="E8">
+        <f>C8*D8</f>
+        <v>-30.166666666666657</v>
+      </c>
+      <c r="F8">
+        <f>C8*C8</f>
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <f>D8*D8</f>
+        <v>227.50694444444431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>71</v>
+      </c>
+      <c r="C9">
+        <f t="shared" ref="C9:C19" si="0">A9-$A$10</f>
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ref="D9:D19" si="1">B9-$B$21</f>
+        <v>-8.0833333333333286</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ref="E9:E19" si="2">C9*D9</f>
+        <v>-8.0833333333333286</v>
+      </c>
+      <c r="F9">
+        <f t="shared" ref="F9:F19" si="3">C9*C9</f>
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <f t="shared" ref="G9:G19" si="4">D9*D9</f>
+        <v>65.3402777777777</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>54</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>-25.083333333333329</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="4"/>
+        <v>629.17361111111086</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>71</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>-8.0833333333333286</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>-32.333333333333314</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="4"/>
+        <v>65.3402777777777</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>93</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>13.916666666666671</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>139.16666666666671</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="4"/>
+        <v>193.67361111111126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>76</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>-3.0833333333333286</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>-24.666666666666629</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="4"/>
+        <v>9.5069444444444144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>87</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>7.9166666666666714</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>158.33333333333343</v>
+      </c>
+      <c r="F14">
+        <f>C14*C14</f>
+        <v>400</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="4"/>
+        <v>62.673611111111185</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15">
+        <v>28</v>
+      </c>
+      <c r="B15">
+        <v>109</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>29.916666666666671</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>747.91666666666674</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="4"/>
+        <v>895.00694444444468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>3.9166666666666714</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>58.750000000000071</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="4"/>
+        <v>15.340277777777814</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <v>75</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>-4.0833333333333286</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>-24.499999999999972</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="4"/>
+        <v>16.673611111111072</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>79</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>-8.3333333333328596E-2</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>-0.74999999999995737</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="3"/>
+        <v>81</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="4"/>
+        <v>6.9444444444436548E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19">
+        <v>87</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>7.9166666666666714</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>79.166666666666714</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="4"/>
+        <v>62.673611111111185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <f>AVERAGE(A8:A19)</f>
+        <v>12.166666666666666</v>
+      </c>
+      <c r="B21">
+        <f>AVERAGE(B8:B19)</f>
+        <v>79.083333333333329</v>
+      </c>
+      <c r="E21">
+        <f>SUM(E8:E19)</f>
+        <v>1062.8333333333337</v>
+      </c>
+      <c r="F21">
+        <f>SUM(F8:F19)</f>
+        <v>1652</v>
+      </c>
+      <c r="G21">
+        <f>SUM(G8:G19)</f>
+        <v>2242.9166666666661</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23">
+        <f>E21/(SQRT(F21*G21))</f>
+        <v>0.55214554965151252</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <f>SQRT(D23^2*(COUNT(A8:A19)-2)/(1-D23^2))</f>
+        <v>2.0942036248035256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27">
+        <v>0.95</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>0.05</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <f>_xlfn.T.DIST.RT(1-B27,COUNT($A$8:$A$19)-2)</f>
+        <v>0.48055349352370058</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28">
+        <v>0.99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>0.01</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <f>_xlfn.T.DIST.RT(1-B28,COUNT($A$8:$A$19)-2)</f>
+        <v>0.49610898749548571</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29">
+        <v>0.999</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29">
+        <v>1E-3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29">
+        <f t="shared" ref="F28:F29" si="5">_xlfn.T.DIST.RT(1-B29,COUNT($A$8:$A$19)-2)</f>
+        <v>0.4996108916873705</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A25:C25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{985DCD50-0835-4F34-ADDA-19C1EB4789AA}">
   <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
       <c r="F1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" t="s">
@@ -1071,7 +1721,7 @@
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D12" t="s">
@@ -1088,31 +1738,31 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="69" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1125,16 +1775,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB48EDA-3491-4432-8C24-8903D395CC0C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="83.88671875" customWidth="1"/>
+    <col min="1" max="1" width="83.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="43.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:1" ht="60">
+      <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1143,703 +1793,708 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="15" width="8.88671875" style="2"/>
-    <col min="16" max="16" width="11.6640625" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="15" width="8.85546875" style="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="5">
         <f>E10/(SQRT(F10*G10))</f>
         <v>0.99749675124293058</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="13">
+      <c r="G1" s="5">
         <f>SQRT(D1^2*(COUNT(A13:A20)-2)/(1-D1^2))</f>
         <v>34.553501996399604</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="17"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="17"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="17"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="8">
         <v>0.95</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="8">
         <v>0.05</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="8">
         <f>_xlfn.T.DIST.RT(1-B5,COUNT($A$13:$A$20)-2)</f>
         <v>0.48087265868734574</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="17"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="8">
         <v>0.99</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="8">
         <v>0.01</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="8">
         <f t="shared" ref="F6:F7" si="0">_xlfn.T.DIST.RT(1-B6,COUNT($A$13:$A$20)-2)</f>
         <v>0.49617274669548816</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="8">
         <v>0.999</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="8">
         <v>1E-3</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="8">
         <f t="shared" si="0"/>
         <v>0.49961726730211037</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="17"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="17"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="9"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16" t="s">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="17"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="15">
+      <c r="A10" s="7">
         <f>AVERAGE(A13:A20)</f>
         <v>5.75</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="8">
         <f>AVERAGE(B13:B20)</f>
         <v>27.912500000000001</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
         <f>SUM(E13:E20)</f>
         <v>18.625000000000007</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="8">
         <f>SUM(F13:F20)</f>
         <v>45.699999999999996</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="8">
         <f>SUM(G13:G20)</f>
         <v>7.6287500000000046</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="17"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="15">
+      <c r="A13" s="7">
         <v>2</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="8">
         <v>26.4</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="8">
         <f>A13-$A$10</f>
         <v>-3.75</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="8">
         <f>B13 -$B$10</f>
         <v>-1.5125000000000028</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="8">
         <f>C13*D13</f>
         <v>5.6718750000000107</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="8">
         <f>C13*C13</f>
         <v>14.0625</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="8">
         <f>D13*D13</f>
         <v>2.2876562500000084</v>
       </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="15">
+      <c r="A14" s="7">
         <v>3.5</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="8">
         <v>26.9</v>
       </c>
-      <c r="C14" s="16">
-        <f t="shared" ref="C14:C20" si="1">A14-$A$10</f>
+      <c r="C14" s="8">
+        <f>A14-$A$10</f>
         <v>-2.25</v>
       </c>
-      <c r="D14" s="16">
-        <f t="shared" ref="D14:D20" si="2">B14 -$B$10</f>
+      <c r="D14" s="8">
+        <f t="shared" ref="D14:D20" si="1">B14 -$B$10</f>
         <v>-1.0125000000000028</v>
       </c>
-      <c r="E14" s="16">
-        <f t="shared" ref="E14:E20" si="3">C14*D14</f>
+      <c r="E14" s="8">
+        <f t="shared" ref="E14:E20" si="2">C14*D14</f>
         <v>2.2781250000000064</v>
       </c>
-      <c r="F14" s="16">
-        <f t="shared" ref="F14:F20" si="4">C14*C14</f>
+      <c r="F14" s="8">
+        <f t="shared" ref="F14:F20" si="3">C14*C14</f>
         <v>5.0625</v>
       </c>
-      <c r="G14" s="16">
-        <f t="shared" ref="G14:G20" si="5">D14*D14</f>
+      <c r="G14" s="8">
+        <f t="shared" ref="G14:G20" si="4">D14*D14</f>
         <v>1.0251562500000058</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="15">
+      <c r="A15" s="7">
         <v>4</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="8">
         <v>27.3</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="8">
+        <f>A15-$A$10</f>
+        <v>-1.75</v>
+      </c>
+      <c r="D15" s="8">
         <f t="shared" si="1"/>
-        <v>-1.75</v>
-      </c>
-      <c r="D15" s="16">
+        <v>-0.61250000000000071</v>
+      </c>
+      <c r="E15" s="8">
         <f t="shared" si="2"/>
-        <v>-0.61250000000000071</v>
-      </c>
-      <c r="E15" s="16">
+        <v>1.0718750000000012</v>
+      </c>
+      <c r="F15" s="8">
         <f t="shared" si="3"/>
-        <v>1.0718750000000012</v>
-      </c>
-      <c r="F15" s="16">
+        <v>3.0625</v>
+      </c>
+      <c r="G15" s="8">
         <f t="shared" si="4"/>
-        <v>3.0625</v>
-      </c>
-      <c r="G15" s="16">
+        <v>0.37515625000000086</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="7">
+        <v>5.2</v>
+      </c>
+      <c r="B16" s="8">
+        <v>27.7</v>
+      </c>
+      <c r="C16" s="8">
+        <f t="shared" ref="C14:C20" si="5">A16-$A$10</f>
+        <v>-0.54999999999999982</v>
+      </c>
+      <c r="D16" s="8">
+        <f t="shared" si="1"/>
+        <v>-0.21250000000000213</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="2"/>
+        <v>0.11687500000000113</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="3"/>
+        <v>0.30249999999999982</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="4"/>
+        <v>4.5156250000000904E-2</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="B17" s="8">
+        <v>28.1</v>
+      </c>
+      <c r="C17" s="8">
         <f t="shared" si="5"/>
-        <v>0.37515625000000086</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="15">
-        <v>5.2</v>
-      </c>
-      <c r="B16" s="16">
-        <v>27.7</v>
-      </c>
-      <c r="C16" s="16">
+        <v>0.54999999999999982</v>
+      </c>
+      <c r="D17" s="8">
         <f t="shared" si="1"/>
-        <v>-0.54999999999999982</v>
-      </c>
-      <c r="D16" s="16">
+        <v>0.1875</v>
+      </c>
+      <c r="E17" s="8">
         <f t="shared" si="2"/>
-        <v>-0.21250000000000213</v>
-      </c>
-      <c r="E16" s="16">
+        <v>0.10312499999999997</v>
+      </c>
+      <c r="F17" s="8">
         <f t="shared" si="3"/>
-        <v>0.11687500000000113</v>
-      </c>
-      <c r="F16" s="16">
+        <v>0.30249999999999982</v>
+      </c>
+      <c r="G17" s="8">
         <f t="shared" si="4"/>
-        <v>0.30249999999999982</v>
-      </c>
-      <c r="G16" s="16">
+        <v>3.515625E-2</v>
+      </c>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="7">
+        <v>7.1</v>
+      </c>
+      <c r="B18" s="8">
+        <v>28.4</v>
+      </c>
+      <c r="C18" s="8">
         <f t="shared" si="5"/>
-        <v>4.5156250000000904E-2</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="15">
-        <v>6.3</v>
-      </c>
-      <c r="B17" s="16">
-        <v>28.1</v>
-      </c>
-      <c r="C17" s="16">
+        <v>1.3499999999999996</v>
+      </c>
+      <c r="D18" s="8">
         <f t="shared" si="1"/>
-        <v>0.54999999999999982</v>
-      </c>
-      <c r="D17" s="16">
+        <v>0.48749999999999716</v>
+      </c>
+      <c r="E18" s="8">
         <f t="shared" si="2"/>
-        <v>0.1875</v>
-      </c>
-      <c r="E17" s="16">
+        <v>0.65812499999999596</v>
+      </c>
+      <c r="F18" s="8">
         <f t="shared" si="3"/>
-        <v>0.10312499999999997</v>
-      </c>
-      <c r="F17" s="16">
+        <v>1.8224999999999991</v>
+      </c>
+      <c r="G18" s="8">
         <f t="shared" si="4"/>
-        <v>0.30249999999999982</v>
-      </c>
-      <c r="G17" s="16">
+        <v>0.23765624999999724</v>
+      </c>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="7">
+        <v>8.4</v>
+      </c>
+      <c r="B19" s="8">
+        <v>29.1</v>
+      </c>
+      <c r="C19" s="8">
         <f t="shared" si="5"/>
-        <v>3.515625E-2</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="15">
-        <v>7.1</v>
-      </c>
-      <c r="B18" s="16">
-        <v>28.4</v>
-      </c>
-      <c r="C18" s="16">
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="D19" s="8">
         <f t="shared" si="1"/>
-        <v>1.3499999999999996</v>
-      </c>
-      <c r="D18" s="16">
+        <v>1.1875</v>
+      </c>
+      <c r="E19" s="8">
         <f t="shared" si="2"/>
-        <v>0.48749999999999716</v>
-      </c>
-      <c r="E18" s="16">
+        <v>3.1468750000000005</v>
+      </c>
+      <c r="F19" s="8">
         <f t="shared" si="3"/>
-        <v>0.65812499999999596</v>
-      </c>
-      <c r="F18" s="16">
+        <v>7.0225000000000017</v>
+      </c>
+      <c r="G19" s="8">
         <f t="shared" si="4"/>
-        <v>1.8224999999999991</v>
-      </c>
-      <c r="G18" s="16">
+        <v>1.41015625</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="B20" s="8">
+        <v>29.4</v>
+      </c>
+      <c r="C20" s="8">
         <f t="shared" si="5"/>
-        <v>0.23765624999999724</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="17"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="15">
-        <v>8.4</v>
-      </c>
-      <c r="B19" s="16">
-        <v>29.1</v>
-      </c>
-      <c r="C19" s="16">
+        <v>3.75</v>
+      </c>
+      <c r="D20" s="8">
         <f t="shared" si="1"/>
-        <v>2.6500000000000004</v>
-      </c>
-      <c r="D19" s="16">
+        <v>1.4874999999999972</v>
+      </c>
+      <c r="E20" s="8">
         <f t="shared" si="2"/>
-        <v>1.1875</v>
-      </c>
-      <c r="E19" s="16">
+        <v>5.5781249999999893</v>
+      </c>
+      <c r="F20" s="8">
         <f t="shared" si="3"/>
-        <v>3.1468750000000005</v>
-      </c>
-      <c r="F19" s="16">
+        <v>14.0625</v>
+      </c>
+      <c r="G20" s="8">
         <f t="shared" si="4"/>
-        <v>7.0225000000000017</v>
-      </c>
-      <c r="G19" s="16">
-        <f t="shared" si="5"/>
-        <v>1.41015625</v>
-      </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="15">
-        <v>9.5</v>
-      </c>
-      <c r="B20" s="16">
-        <v>29.4</v>
-      </c>
-      <c r="C20" s="16">
-        <f t="shared" si="1"/>
-        <v>3.75</v>
-      </c>
-      <c r="D20" s="16">
-        <f t="shared" si="2"/>
-        <v>1.4874999999999972</v>
-      </c>
-      <c r="E20" s="16">
-        <f t="shared" si="3"/>
-        <v>5.5781249999999893</v>
-      </c>
-      <c r="F20" s="16">
-        <f t="shared" si="4"/>
-        <v>14.0625</v>
-      </c>
-      <c r="G20" s="16">
-        <f t="shared" si="5"/>
         <v>2.2126562499999913</v>
       </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" spans="1:18" ht="15" thickBot="1">
-      <c r="A21" s="20"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" thickBot="1">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="12"/>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="31" spans="1:18">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="6"/>
+      <c r="A32" s="3"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-    </row>
-    <row r="40" spans="1:12" ht="15.6">
-      <c r="A40" s="10" t="s">
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+    </row>
+    <row r="40" spans="1:12" ht="15.75">
+      <c r="A40" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="6"/>
+      <c r="A41" s="3"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A23:R23"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A27:P27"/>
     <mergeCell ref="A44:K44"/>
     <mergeCell ref="A46:L46"/>
     <mergeCell ref="A29:G29"/>
@@ -1849,11 +2504,6 @@
     <mergeCell ref="A37:L37"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A23:R23"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A27:P27"/>
     <mergeCell ref="A31:I31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
